--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11475,14 +11475,14 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
         <v>12062000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>24124</v>
+        <v>24172</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>12062000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>24124</v>
+        <v>24172</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18014,34 +18014,34 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>8631000</v>
+        <v>7596000</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>26721</v>
+        <v>23517</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K269" s="5" t="n">
-        <v>7595280</v>
+        <v>7596000</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>23515</v>
+        <v>23517</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -18081,7 +18081,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19353,7 +19353,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21013,7 +21013,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21776,38 +21776,30 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H328" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I328" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H328" s="5" t="n">
+        <v>12273000</v>
+      </c>
+      <c r="I328" s="5" t="n">
+        <v>25201</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K328" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L328" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K328" s="5" t="n">
+        <v>12273000</v>
+      </c>
+      <c r="L328" s="5" t="n">
+        <v>25201</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -21816,7 +21808,7 @@
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21900,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22045,7 +22037,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22107,7 +22099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22169,7 +22161,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22231,7 +22223,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22363,7 +22355,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22482,7 +22474,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -22619,7 +22611,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22681,7 +22673,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22743,7 +22735,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22805,7 +22797,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22937,7 +22929,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23056,7 +23048,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -23193,7 +23185,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -23255,7 +23247,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23317,7 +23309,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23379,7 +23371,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -23511,7 +23503,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23573,7 +23565,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23630,34 +23622,34 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
-        <v>6515000</v>
+        <v>5734000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>25956</v>
+        <v>22845</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K357" s="5" t="n">
-        <v>5733200</v>
+        <v>5734000</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>22841</v>
+        <v>22845</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N357" s="3" t="inlineStr">
@@ -23767,7 +23759,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23829,7 +23821,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23891,7 +23883,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23953,7 +23945,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -24212,34 +24204,34 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
-        <v>6495000</v>
+        <v>5716000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>25876</v>
+        <v>22773</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>5715600</v>
+        <v>5716000</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>22771</v>
+        <v>22773</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -24349,7 +24341,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24411,7 +24403,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24473,7 +24465,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24535,7 +24527,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24931,7 +24923,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24993,7 +24985,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -25055,7 +25047,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -25117,7 +25109,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25513,7 +25505,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25575,7 +25567,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25637,7 +25629,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25699,7 +25691,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26165,7 +26157,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -26227,7 +26219,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -26289,7 +26281,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -26561,7 +26553,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -26623,7 +26615,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26685,7 +26677,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26747,7 +26739,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26809,7 +26801,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26933,7 +26925,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -27130,7 +27122,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -27197,7 +27189,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -27259,7 +27251,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -27321,7 +27313,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -27383,7 +27375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -27445,7 +27437,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -27569,7 +27561,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -27766,7 +27758,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -27833,7 +27825,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -27895,7 +27887,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27957,7 +27949,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -28019,7 +28011,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -28081,7 +28073,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -28205,7 +28197,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -28267,7 +28259,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -28394,7 +28386,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -28461,7 +28453,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -28523,7 +28515,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -28585,7 +28577,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -28647,7 +28639,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -28709,7 +28701,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -28833,7 +28825,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -28895,7 +28887,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -29022,7 +29014,7 @@
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -29089,7 +29081,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -29151,7 +29143,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -29213,7 +29205,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -29275,7 +29267,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -29337,7 +29329,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -29394,7 +29386,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -29461,7 +29453,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -29523,7 +29515,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -29650,7 +29642,7 @@
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
@@ -29717,7 +29709,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -29779,7 +29771,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -29841,7 +29833,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -29903,7 +29895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29965,7 +29957,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -30022,7 +30014,7 @@
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -30089,7 +30081,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -30151,7 +30143,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -30213,7 +30205,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -30270,7 +30262,7 @@
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -30337,7 +30329,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -30399,7 +30391,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -30461,7 +30453,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -30523,7 +30515,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -30585,7 +30577,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -30642,7 +30634,7 @@
       </c>
       <c r="F467" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -30709,7 +30701,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -30771,7 +30763,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -30828,38 +30820,30 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H470" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I470" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H470" s="5" t="n">
+        <v>15433000</v>
+      </c>
+      <c r="I470" s="5" t="n">
+        <v>24892</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K470" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L470" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K470" s="5" t="n">
+        <v>15433000</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>24892</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
@@ -30868,7 +30852,7 @@
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30898,7 +30882,7 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -30965,7 +30949,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -31027,7 +31011,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -31089,7 +31073,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -31151,7 +31135,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -31213,7 +31197,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -31270,7 +31254,7 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -31337,7 +31321,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -31399,7 +31383,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -31461,7 +31445,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -31523,7 +31507,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -31585,7 +31569,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -31647,7 +31631,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -31709,7 +31693,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -31771,7 +31755,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -31833,7 +31817,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -31890,7 +31874,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -31957,7 +31941,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -32019,7 +32003,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -32081,7 +32065,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -32143,7 +32127,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -32205,7 +32189,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -32267,7 +32251,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -32329,7 +32313,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -32391,7 +32375,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -32453,7 +32437,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -32577,7 +32561,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -32639,7 +32623,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2022-11-24</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -32701,7 +32685,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -32763,7 +32747,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -32825,7 +32809,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -32887,7 +32871,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -32949,7 +32933,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -33011,7 +32995,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -33073,7 +33057,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -33197,7 +33181,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -33259,7 +33243,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -33316,38 +33300,30 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H510" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I510" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H510" s="5" t="n">
+        <v>15249000</v>
+      </c>
+      <c r="I510" s="5" t="n">
+        <v>24595</v>
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K510" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L510" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K510" s="5" t="n">
+        <v>15249000</v>
+      </c>
+      <c r="L510" s="5" t="n">
+        <v>24595</v>
       </c>
       <c r="M510" s="3" t="inlineStr">
         <is>
@@ -33356,7 +33332,7 @@
       </c>
       <c r="N510" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33391,7 +33367,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -33453,7 +33429,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -33515,7 +33491,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -33577,7 +33553,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -33639,7 +33615,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -33701,7 +33677,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -33825,7 +33801,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -33887,7 +33863,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -33949,7 +33925,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -34011,7 +33987,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -34073,7 +34049,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -34135,7 +34111,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -34197,7 +34173,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -34259,7 +34235,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -34321,7 +34297,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -34445,7 +34421,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -34507,7 +34483,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -34564,7 +34540,7 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -34639,7 +34615,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -34701,7 +34677,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -34763,7 +34739,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -34825,7 +34801,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -34887,7 +34863,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -34949,7 +34925,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -35006,7 +34982,7 @@
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
@@ -35073,7 +35049,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -35135,7 +35111,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -35197,7 +35173,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -35259,7 +35235,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -35321,7 +35297,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -35383,7 +35359,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -35445,7 +35421,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -35507,7 +35483,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -35569,7 +35545,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -35626,7 +35602,7 @@
       </c>
       <c r="F547" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
@@ -35693,7 +35669,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -35755,7 +35731,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -35812,38 +35788,30 @@
       </c>
       <c r="F550" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H550" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I550" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H550" s="5" t="n">
+        <v>15022000</v>
+      </c>
+      <c r="I550" s="5" t="n">
+        <v>24229</v>
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K550" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L550" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K550" s="5" t="n">
+        <v>15022000</v>
+      </c>
+      <c r="L550" s="5" t="n">
+        <v>24229</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
@@ -35852,7 +35820,7 @@
       </c>
       <c r="N550" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35887,7 +35855,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -35949,7 +35917,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -36011,7 +35979,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -36073,7 +36041,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -36135,7 +36103,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -36197,7 +36165,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -36254,7 +36222,7 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
@@ -36321,7 +36289,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -36383,7 +36351,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -36445,7 +36413,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -36507,7 +36475,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -36569,7 +36537,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -36631,7 +36599,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -36693,7 +36661,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -36755,7 +36723,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -36817,7 +36785,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -36874,7 +36842,7 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
@@ -36941,7 +36909,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -37003,7 +36971,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -37065,7 +37033,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -37127,7 +37095,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -37189,7 +37157,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -37251,7 +37219,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -37313,7 +37281,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -37375,7 +37343,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -37437,7 +37405,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -37494,7 +37462,7 @@
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
@@ -37561,7 +37529,7 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H578" s="5" t="n">
@@ -37623,7 +37591,7 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H579" s="5" t="n">
@@ -37685,7 +37653,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -37747,7 +37715,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -37809,7 +37777,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -37871,7 +37839,7 @@
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H583" s="5" t="n">
@@ -37933,7 +37901,7 @@
       </c>
       <c r="G584" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H584" s="5" t="n">
@@ -37995,7 +37963,7 @@
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H585" s="5" t="n">
@@ -38057,7 +38025,7 @@
       </c>
       <c r="G586" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H586" s="5" t="n">
@@ -38181,7 +38149,7 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
@@ -38243,7 +38211,7 @@
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="H589" s="5" t="n">
@@ -38305,7 +38273,7 @@
       </c>
       <c r="G590" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H590" s="5" t="n">
@@ -38367,7 +38335,7 @@
       </c>
       <c r="G591" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H591" s="5" t="n">
@@ -38429,7 +38397,7 @@
       </c>
       <c r="G592" s="3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="H592" s="5" t="n">
@@ -38491,7 +38459,7 @@
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H593" s="5" t="n">
@@ -38553,7 +38521,7 @@
       </c>
       <c r="G594" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H594" s="5" t="n">
@@ -38615,7 +38583,7 @@
       </c>
       <c r="G595" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H595" s="5" t="n">
@@ -38677,7 +38645,7 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H596" s="5" t="n">
@@ -38801,7 +38769,7 @@
       </c>
       <c r="G598" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H598" s="5" t="n">
@@ -38863,7 +38831,7 @@
       </c>
       <c r="G599" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H599" s="5" t="n">
@@ -38925,7 +38893,7 @@
       </c>
       <c r="G600" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H600" s="5" t="n">
@@ -38987,7 +38955,7 @@
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H601" s="5" t="n">
@@ -39049,7 +39017,7 @@
       </c>
       <c r="G602" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H602" s="5" t="n">
@@ -39111,7 +39079,7 @@
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H603" s="5" t="n">
@@ -39173,7 +39141,7 @@
       </c>
       <c r="G604" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H604" s="5" t="n">
@@ -39235,7 +39203,7 @@
       </c>
       <c r="G605" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H605" s="5" t="n">
@@ -39297,7 +39265,7 @@
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H606" s="5" t="n">
@@ -39421,7 +39389,7 @@
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H608" s="5" t="n">
@@ -39483,7 +39451,7 @@
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="H609" s="5" t="n">
@@ -39545,7 +39513,7 @@
       </c>
       <c r="G610" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H610" s="5" t="n">
@@ -39602,34 +39570,34 @@
       </c>
       <c r="F611" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="H611" s="5" t="n">
-        <v>9029000</v>
+        <v>7946000</v>
       </c>
       <c r="I611" s="5" t="n">
-        <v>27444</v>
+        <v>24152</v>
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K611" s="5" t="n">
-        <v>7945520</v>
+        <v>7946000</v>
       </c>
       <c r="L611" s="5" t="n">
-        <v>24151</v>
+        <v>24152</v>
       </c>
       <c r="M611" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N611" s="3" t="inlineStr">
@@ -39669,7 +39637,7 @@
       </c>
       <c r="G612" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H612" s="5" t="n">
@@ -39731,7 +39699,7 @@
       </c>
       <c r="G613" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H613" s="5" t="n">
@@ -39793,7 +39761,7 @@
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H614" s="5" t="n">
@@ -39855,7 +39823,7 @@
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H615" s="5" t="n">
@@ -39917,7 +39885,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -40041,7 +40009,7 @@
       </c>
       <c r="G618" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H618" s="5" t="n">
@@ -40103,7 +40071,7 @@
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H619" s="5" t="n">
@@ -40222,7 +40190,7 @@
       </c>
       <c r="F621" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G621" s="3" t="inlineStr">
@@ -40289,7 +40257,7 @@
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H622" s="5" t="n">
@@ -40351,7 +40319,7 @@
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H623" s="5" t="n">
@@ -40413,7 +40381,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
@@ -40475,7 +40443,7 @@
       </c>
       <c r="G625" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H625" s="5" t="n">
@@ -40537,7 +40505,7 @@
       </c>
       <c r="G626" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H626" s="5" t="n">
@@ -40661,7 +40629,7 @@
       </c>
       <c r="G628" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H628" s="5" t="n">
@@ -40723,7 +40691,7 @@
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H629" s="5" t="n">
@@ -40842,7 +40810,7 @@
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
@@ -40909,7 +40877,7 @@
       </c>
       <c r="G632" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H632" s="5" t="n">
@@ -40971,7 +40939,7 @@
       </c>
       <c r="G633" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H633" s="5" t="n">
@@ -41033,7 +41001,7 @@
       </c>
       <c r="G634" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H634" s="5" t="n">
@@ -41095,7 +41063,7 @@
       </c>
       <c r="G635" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H635" s="5" t="n">
@@ -41157,7 +41125,7 @@
       </c>
       <c r="G636" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H636" s="5" t="n">
@@ -41281,7 +41249,7 @@
       </c>
       <c r="G638" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H638" s="5" t="n">
@@ -41343,7 +41311,7 @@
       </c>
       <c r="G639" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H639" s="5" t="n">
@@ -41462,7 +41430,7 @@
       </c>
       <c r="F641" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G641" s="3" t="inlineStr">
@@ -41529,7 +41497,7 @@
       </c>
       <c r="G642" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H642" s="5" t="n">
@@ -41591,7 +41559,7 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
@@ -41653,7 +41621,7 @@
       </c>
       <c r="G644" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H644" s="5" t="n">
@@ -41715,7 +41683,7 @@
       </c>
       <c r="G645" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H645" s="5" t="n">
@@ -41777,7 +41745,7 @@
       </c>
       <c r="G646" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H646" s="5" t="n">
@@ -41901,7 +41869,7 @@
       </c>
       <c r="G648" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H648" s="5" t="n">
@@ -41963,7 +41931,7 @@
       </c>
       <c r="G649" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H649" s="5" t="n">
@@ -42208,7 +42176,7 @@
           <t>A | 1335呎 (4+房)
 $4168万
 $31,221/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -42257,7 +42225,7 @@
           <t>A | 716呎 (3房)
 $1890万
 $26,391/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -42265,7 +42233,7 @@
           <t>B | 661呎 (3房)
 $1724万
 $26,080/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -42273,7 +42241,7 @@
           <t>C | 485呎 (2房)
 $1284万
 $26,480/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -42281,7 +42249,7 @@
           <t>D | 318呎 (1房)
 $733万
 $23,044/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -42305,7 +42273,7 @@
           <t>G | 499呎 (2房)
 $1283万
 $25,711/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -42320,7 +42288,7 @@
           <t>A | 716呎 (3房)
 $1884万
 $26,313/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -42328,7 +42296,7 @@
           <t>B | 661呎 (3房)
 $1719万
 $26,002/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -42336,7 +42304,7 @@
           <t>C | 485呎 (2房)
 $1280万
 $26,402/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -42344,7 +42312,7 @@
           <t>D | 318呎 (1房)
 $731万
 $22,975/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -42368,7 +42336,7 @@
           <t>G | 499呎 (2房)
 $1280万
 $25,647/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -42383,7 +42351,7 @@
           <t>A | 716呎 (3房)
 $1873万
 $26,155/呎
-(24年-07月-25日)</t>
+(24年-07月-26日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -42391,7 +42359,7 @@
           <t>B | 661呎 (3房)
 $1708万
 $25,846/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -42399,7 +42367,7 @@
           <t>C | 485呎 (2房)
 $1273万
 $26,245/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -42407,7 +42375,7 @@
           <t>D | 318呎 (1房)
 $726万
 $22,836/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -42431,7 +42399,7 @@
           <t>G | 499呎 (2房)
 $1268万
 $25,417/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -42446,7 +42414,7 @@
           <t>A | 716呎 (3房)
 $1867万
 $26,077/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -42454,7 +42422,7 @@
           <t>B | 661呎 (3房)
 $1703万
 $25,769/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -42462,7 +42430,7 @@
           <t>C | 485呎 (2房)
 $1269万
 $26,167/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -42470,7 +42438,7 @@
           <t>D | 318呎 (1房)
 $724万
 $22,770/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -42494,7 +42462,7 @@
           <t>G | 499呎 (2房)
 $1264万
 $25,341/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -42509,7 +42477,7 @@
           <t>A | 716呎 (3房)
 $1862万
 $25,999/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -42517,7 +42485,7 @@
           <t>B | 661呎 (3房)
 $1698万
 $25,691/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -42525,7 +42493,7 @@
           <t>C | 485呎 (2房)
 $1265万
 $26,087/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -42533,7 +42501,7 @@
           <t>D | 318呎 (1房)
 $722万
 $22,701/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -42557,7 +42525,7 @@
           <t>G | 499呎 (2房)
 $1261万
 $25,265/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -42572,7 +42540,7 @@
           <t>A | 716呎 (3房)
 $1856万
 $25,922/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42580,7 +42548,7 @@
           <t>B | 661呎 (3房)
 $1693万
 $25,616/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -42588,7 +42556,7 @@
           <t>C | 485呎 (2房)
 $1261万
 $26,008/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -42596,7 +42564,7 @@
           <t>D | 318呎 (1房)
 $720万
 $22,635/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -42620,7 +42588,7 @@
           <t>G | 499呎 (2房)
 $1264万
 $25,327/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -42635,7 +42603,7 @@
           <t>A | 716呎 (3房)
 $1850万
 $25,842/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42643,7 +42611,7 @@
           <t>B | 661呎 (3房)
 $1688万
 $25,539/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -42651,7 +42619,7 @@
           <t>C | 485呎 (2房)
 $1258万
 $25,932/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -42659,7 +42627,7 @@
           <t>D | 318呎 (1房)
 $718万
 $22,566/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -42683,7 +42651,7 @@
           <t>G | 499呎 (2房)
 $1260万
 $25,261/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42666,7 @@
           <t>A | 716呎 (3房)
 $1845万
 $25,767/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -42706,7 +42674,7 @@
           <t>B | 661呎 (3房)
 $1683万
 $25,461/呎
-(24年-07月-10日)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -42714,7 +42682,7 @@
           <t>C | 485呎 (2房)
 $1254万
 $25,856/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -42722,7 +42690,7 @@
           <t>D | 318呎 (1房)
 $716万
 $22,500/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -42746,7 +42714,7 @@
           <t>G | 499呎 (2房)
 $1257万
 $25,196/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -42761,7 +42729,7 @@
           <t>A | 716呎 (3房)
 $1839万
 $25,689/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42769,7 +42737,7 @@
           <t>B | 661呎 (3房)
 $1678万
 $25,386/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -42777,7 +42745,7 @@
           <t>C | 485呎 (2房)
 $1250万
 $25,777/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -42785,7 +42753,7 @@
           <t>D | 318呎 (1房)
 $713万
 $22,431/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -42801,7 +42769,7 @@
           <t>F | 448呎 (2房)
 $1048万
 $23,400/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -42809,7 +42777,7 @@
           <t>G | 499呎 (2房)
 $1246万
 $24,966/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -42824,7 +42792,7 @@
           <t>A | 716呎 (3房)
 $1834万
 $25,612/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -42832,7 +42800,7 @@
           <t>B | 661呎 (3房)
 $1673万
 $25,310/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -42840,7 +42808,7 @@
           <t>C | 485呎 (2房)
 $1246万
 $25,701/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -42848,7 +42816,7 @@
           <t>D | 318呎 (1房)
 $711万
 $22,365/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -42872,7 +42840,7 @@
           <t>G | 499呎 (2房)
 $1242万
 $24,890/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -42887,7 +42855,7 @@
           <t>A | 716呎 (3房)
 $1828万
 $25,535/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -42895,7 +42863,7 @@
           <t>B | 661呎 (3房)
 $1668万
 $25,234/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -42903,7 +42871,7 @@
           <t>C | 486呎 (2房)
 $1243万
 $25,570/呎
-(22年-10月-05日)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -42911,7 +42879,7 @@
           <t>D | 318呎 (1房)
 $709万
 $22,299/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -42935,7 +42903,7 @@
           <t>G | 499呎 (2房)
 $1238万
 $24,816/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -42950,7 +42918,7 @@
           <t>A | 716呎 (3房)
 $1817万
 $25,383/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -42958,7 +42926,7 @@
           <t>B | 661呎 (3房)
 $1658万
 $25,085/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -42966,7 +42934,7 @@
           <t>C | 485呎 (2房)
 $1235万
 $25,470/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -42974,7 +42942,7 @@
           <t>D | 318呎 (1房)
 $705万
 $22,164/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -42998,7 +42966,7 @@
           <t>G | 499呎 (2房)
 $1231万
 $24,667/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -43013,7 +42981,7 @@
           <t>A | 716呎 (3房)
 $1812万
 $25,307/呎
-(24年-07月-23日)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43021,7 +42989,7 @@
           <t>B | 661呎 (3房)
 $1653万
 $25,008/呎
-(25年-03月-04日)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -43029,7 +42997,7 @@
           <t>C | 485呎 (2房)
 $1232万
 $25,394/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -43037,7 +43005,7 @@
           <t>D | 318呎 (1房)
 $723万
 $22,726/呎
-(22年-10月-06日)</t>
+(22年-10月-07日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -43061,7 +43029,7 @@
           <t>G | 499呎 (2房)
 $1227万
 $24,593/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -43076,7 +43044,7 @@
           <t>A | 716呎 (3房)
 $1807万
 $25,232/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43084,7 +43052,7 @@
           <t>B | 661呎 (3房)
 $1648万
 $24,933/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -43092,7 +43060,7 @@
           <t>C | 485呎 (2房)
 $1228万
 $25,318/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -43100,7 +43068,7 @@
           <t>D | 318呎 (1房)
 $701万
 $22,031/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -43124,7 +43092,7 @@
           <t>G | 499呎 (2房)
 $1224万
 $24,521/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -43139,7 +43107,7 @@
           <t>A | 716呎 (3房)
 $1801万
 $25,155/呎
-(24年-07月-25日)</t>
+(24年-07月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -43147,7 +43115,7 @@
           <t>B | 661呎 (3房)
 $1643万
 $24,859/呎
-(24年-09月-22日)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -43155,7 +43123,7 @@
           <t>C | 485呎 (2房)
 $1224万
 $25,243/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -43163,7 +43131,7 @@
           <t>D | 318呎 (1房)
 $698万
 $21,965/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -43187,7 +43155,7 @@
           <t>G | 499呎 (2房)
 $1234万
 $24,727/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -43202,7 +43170,7 @@
           <t>A | 716呎 (3房)
 $1796万
 $25,081/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43210,7 +43178,7 @@
           <t>B | 661呎 (3房)
 $1692万
 $25,601/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -43218,7 +43186,7 @@
           <t>C | 485呎 (2房)
 $1221万
 $25,167/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -43226,7 +43194,7 @@
           <t>D | 318呎 (1房)
 $696万
 $21,903/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -43250,7 +43218,7 @@
           <t>G | 499呎 (2房)
 $1231万
 $24,667/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -43265,7 +43233,7 @@
           <t>A | 716呎 (3房)
 $1790万
 $25,006/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43273,7 +43241,7 @@
           <t>B | 661呎 (3房)
 $1633万
 $24,711/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -43281,7 +43249,7 @@
           <t>C | 486呎 (2房)
 $1217万
 $25,039/呎
-(23年-02月-12日)</t>
+(23年-02月-13日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -43289,7 +43257,7 @@
           <t>D | 318呎 (1房)
 $694万
 $21,836/呎
-(22年-10月-02日)</t>
+(22年-10月-03日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43313,7 +43281,7 @@
           <t>G | 499呎 (2房)
 $1213万
 $24,301/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -43328,7 +43296,7 @@
           <t>A | 716呎 (3房)
 $1785万
 $24,930/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43336,7 +43304,7 @@
           <t>B | 661呎 (3房)
 $1628万
 $24,637/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -43344,7 +43312,7 @@
           <t>C | 485呎 (2房)
 $1213万
 $25,016/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -43352,7 +43320,7 @@
           <t>D | 318呎 (1房)
 $692万
 $21,770/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43376,7 +43344,7 @@
           <t>G | 499呎 (2房)
 $1209万
 $24,228/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43359,7 @@
           <t>A | 716呎 (3房)
 $1780万
 $24,858/呎
-(24年-08月-22日)</t>
+(24年-08月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43399,7 +43367,7 @@
           <t>B | 661呎 (3房)
 $1624万
 $24,563/呎
-(24年-10月-13日)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -43407,7 +43375,7 @@
           <t>C | 485呎 (2房)
 $1210万
 $24,942/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -43415,7 +43383,7 @@
           <t>D | 318呎 (1房)
 $690万
 $21,704/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -43439,7 +43407,7 @@
           <t>G | 499呎 (2房)
 $1205万
 $24,156/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -43454,7 +43422,7 @@
           <t>A | 716呎 (3房)
 $1769万
 $24,708/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43462,7 +43430,7 @@
           <t>B | 661呎 (3房)
 $1614万
 $24,418/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -43470,7 +43438,7 @@
           <t>C | 485呎 (2房)
 $1202万
 $24,794/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -43478,7 +43446,7 @@
           <t>D | 318呎 (1房)
 $686万
 $21,575/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -43502,7 +43470,7 @@
           <t>G | 499呎 (2房)
 $1218万
 $24,407/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43485,7 @@
           <t>A | 716呎 (3房)
 $1764万
 $24,634/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43525,7 +43493,7 @@
           <t>B | 661呎 (3房)
 $1609万
 $24,343/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -43533,7 +43501,7 @@
           <t>C | 485呎 (2房)
 $1199万
 $24,720/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -43541,7 +43509,7 @@
           <t>D | 318呎 (1房)
 $704万
 $22,123/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -43565,7 +43533,7 @@
           <t>G | 499呎 (2房)
 $1215万
 $24,349/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -43580,7 +43548,7 @@
           <t>A | 716呎 (3房)
 $1759万
 $24,561/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43588,7 +43556,7 @@
           <t>B | 661呎 (3房)
 $1604万
 $24,271/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -43596,7 +43564,7 @@
           <t>C | 485呎 (2房)
 $1195万
 $24,645/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -43604,7 +43572,7 @@
           <t>D | 318呎 (1房)
 $682万
 $21,447/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -43628,7 +43596,7 @@
           <t>G | 499呎 (2房)
 $1212万
 $24,291/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -43643,7 +43611,7 @@
           <t>A | 716呎 (3房)
 $1753万
 $24,487/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43651,7 +43619,7 @@
           <t>B | 661呎 (3房)
 $1600万
 $24,198/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -43659,7 +43627,7 @@
           <t>C | 485呎 (2房)
 $1192万
 $24,571/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -43667,7 +43635,7 @@
           <t>D | 318呎 (1房)
 $680万
 $21,381/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -43691,7 +43659,7 @@
           <t>G | 499呎 (2房)
 $1209万
 $24,230/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -43706,7 +43674,7 @@
           <t>A | 716呎 (3房)
 $1748万
 $24,415/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43714,7 +43682,7 @@
           <t>B | 661呎 (3房)
 $1595万
 $24,126/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -43722,7 +43690,7 @@
           <t>C | 485呎 (2房)
 $1188万
 $24,497/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -43751,10 +43719,10 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>G | 500呎 (2房)
+          <t>G | 499呎 (2房)
 $1206万
-$24,124/呎
-(26年-06月-26日)</t>
+$24,172/呎
+(26年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -43835,17 +43803,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43946,7 +43914,7 @@
           <t>D | 457呎 (2房)
 $1090万
 $23,840/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
@@ -44025,7 +43993,7 @@
           <t>D | 457呎 (2房)
 $1087万
 $23,783/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -44096,7 +44064,7 @@
           <t>C | 463呎 (2房)
 $1068万
 $23,076/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -44104,7 +44072,7 @@
           <t>D | 457呎 (2房)
 $1085万
 $23,740/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -44159,7 +44127,7 @@
           <t>A | 487呎 (2房)
 $1264万
 $25,947/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -44183,7 +44151,7 @@
           <t>D | 457呎 (2房)
 $1080万
 $23,637/呎
-(26年-07月-08日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -44238,7 +44206,7 @@
           <t>A | 487呎 (2房)
 $1260万
 $25,871/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -44262,7 +44230,7 @@
           <t>D | 457呎 (2房)
 $1078万
 $23,580/呎
-(26年-07月-01日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -44317,7 +44285,7 @@
           <t>A | 487呎 (2房)
 $1256万
 $25,793/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -44333,7 +44301,7 @@
           <t>C | 463呎 (2房)
 $1054万
 $22,760/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -44341,7 +44309,7 @@
           <t>D | 457呎 (2房)
 $1069万
 $23,396/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -44349,7 +44317,7 @@
           <t>E | 250呎 (开放式)
 $590万
 $23,580/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -44412,7 +44380,7 @@
           <t>C | 463呎 (2房)
 $1051万
 $22,691/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -44420,7 +44388,7 @@
           <t>D | 457呎 (2房)
 $1066万
 $23,324/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -44428,7 +44396,7 @@
           <t>E | 250呎 (开放式)
 $588万
 $23,508/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
@@ -44491,7 +44459,7 @@
           <t>C | 463呎 (2房)
 $1047万
 $22,622/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -44499,7 +44467,7 @@
           <t>D | 457呎 (2房)
 $1063万
 $23,254/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -44507,15 +44475,15 @@
           <t>E | 250呎 (开放式)
 $586万
 $23,440/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $871万
 $26,963/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -44570,7 +44538,7 @@
           <t>C | 463呎 (2房)
 $1044万
 $22,555/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -44578,7 +44546,7 @@
           <t>D | 457呎 (2房)
 $1060万
 $23,186/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -44586,15 +44554,15 @@
           <t>E | 250呎 (开放式)
 $584万
 $23,368/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $868万
 $26,882/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -44633,7 +44601,7 @@
           <t>A | 487呎 (2房)
 $1242万
 $25,503/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -44649,7 +44617,7 @@
           <t>C | 463呎 (2房)
 $1041万
 $22,488/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -44657,7 +44625,7 @@
           <t>D | 457呎 (2房)
 $1056万
 $23,116/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -44665,15 +44633,15 @@
           <t>E | 250呎 (开放式)
 $582万
 $23,296/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $866万
 $26,802/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -44697,7 +44665,7 @@
           <t>J | 459呎 (2房)
 $1070万
 $23,305/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -44712,7 +44680,7 @@
           <t>A | 487呎 (2房)
 $1237万
 $25,409/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -44728,7 +44696,7 @@
           <t>C | 463呎 (2房)
 $1038万
 $22,421/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -44736,7 +44704,7 @@
           <t>D | 457呎 (2房)
 $1053万
 $23,046/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -44744,15 +44712,15 @@
           <t>E | 250呎 (开放式)
 $581万
 $23,232/呎
-(24年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
+(24年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$863万
-$26,721/呎
-(已定价未售)</t>
+$760万
+$23,517/呎
+(26年-07月-26日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -44776,7 +44744,7 @@
           <t>J | 459呎 (2房)
 $1066万
 $23,235/呎
-(26年-06月-20日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -44791,7 +44759,7 @@
           <t>A | 487呎 (2房)
 $1234万
 $25,333/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -44807,7 +44775,7 @@
           <t>C | 463呎 (2房)
 $1035万
 $22,354/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -44815,7 +44783,7 @@
           <t>D | 457呎 (2房)
 $1050万
 $22,978/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -44823,15 +44791,15 @@
           <t>E | 250呎 (开放式)
 $579万
 $23,160/呎
-(26年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $860万
 $26,641/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -44855,7 +44823,7 @@
           <t>J | 459呎 (2房)
 $1063万
 $23,166/呎
-(26年-06月-23日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -44870,7 +44838,7 @@
           <t>A | 487呎 (2房)
 $1226万
 $25,181/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -44886,7 +44854,7 @@
           <t>C | 463呎 (2房)
 $1029万
 $22,222/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -44894,7 +44862,7 @@
           <t>D | 457呎 (2房)
 $1044万
 $22,840/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -44902,15 +44870,15 @@
           <t>E | 250呎 (开放式)
 $576万
 $23,024/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $855万
 $26,483/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -44949,7 +44917,7 @@
           <t>A | 487呎 (2房)
 $1236万
 $25,382/呎
-(26年-06月-23日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -44965,7 +44933,7 @@
           <t>C | 463呎 (2房)
 $1026万
 $22,156/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -44973,7 +44941,7 @@
           <t>D | 457呎 (2房)
 $1041万
 $22,772/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -44981,7 +44949,7 @@
           <t>E | 250呎 (开放式)
 $574万
 $22,952/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -44989,7 +44957,7 @@
           <t>F | 323呎 (1房)
 $772万
 $23,895/呎
-(22年-10月-02日)</t>
+(22年-10月-03日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -45000,12 +44968,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $688万
 $27,402/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -45013,7 +44981,7 @@
           <t>J | 459呎 (2房)
 $1054万
 $22,959/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -45028,7 +44996,7 @@
           <t>A | 487呎 (2房)
 $1233万
 $25,322/呎
-(26年-06月-27日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -45044,7 +45012,7 @@
           <t>C | 463呎 (2房)
 $1023万
 $22,089/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -45052,7 +45020,7 @@
           <t>D | 457呎 (2房)
 $1038万
 $22,705/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -45060,7 +45028,7 @@
           <t>E | 250呎 (开放式)
 $588万
 $23,536/呎
-(22年-10月-05日)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -45068,7 +45036,7 @@
           <t>F | 323呎 (1房)
 $748万
 $23,167/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -45079,12 +45047,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $686万
 $27,319/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -45092,7 +45060,7 @@
           <t>J | 459呎 (2房)
 $1080万
 $23,540/呎
-(22年-09月-29日)</t>
+(22年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -45107,7 +45075,7 @@
           <t>A | 487呎 (2房)
 $1230万
 $25,261/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -45123,7 +45091,7 @@
           <t>C | 463呎 (2房)
 $1020万
 $22,022/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -45131,7 +45099,7 @@
           <t>D | 457呎 (2房)
 $1064万
 $23,280/呎
-(22年-10月-06日)</t>
+(22年-10月-07日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -45139,7 +45107,7 @@
           <t>E | 250呎 (开放式)
 $587万
 $23,464/呎
-(22年-10月-05日)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -45147,7 +45115,7 @@
           <t>F | 323呎 (1房)
 $746万
 $23,096/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -45158,12 +45126,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $684万
 $27,239/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -45171,7 +45139,7 @@
           <t>J | 459呎 (2房)
 $1048万
 $22,821/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -45181,7 +45149,323 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1227万
+$25,201/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1016万
+$21,955/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1172万
+$25,646/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$569万
+$22,748/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$845万
+$26,167/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$682万
+$27,155/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1044万
+$22,752/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1208万
+$24,807/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1014万
+$21,890/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1058万
+$23,140/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$567万
+$22,680/呎
+(24年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$742万
+$22,960/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$680万
+$27,076/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1183万
+$25,778/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1204万
+$24,733/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1010万
+$21,825/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1025万
+$22,433/呎
+(24年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$565万
+$22,612/呎
+(26年-03月-16日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$739万
+$22,892/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$678万
+$26,992/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1180万
+$25,699/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1201万
+$24,661/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1008万
+$21,760/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1022万
+$22,368/呎
+(24年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$564万
+$22,544/呎
+(26年-03月-24日)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$758万
+$23,471/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$665万
+$26,510/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1158万
+$25,240/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -45189,7 +45473,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45197,39 +45481,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
+$1004万
+$21,685/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
 $1016万
-$21,955/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1172万
-$25,646/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
+$22,234/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$569万
-$22,748/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="inlineStr">
+$560万
+$22,412/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$845万
-$26,167/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+$733万
+$22,687/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45237,38 +45521,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$682万
-$27,155/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
+$573万
+$22,845/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1044万
-$22,752/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+$998万
+$21,747/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1208万
-$24,807/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45276,39 +45560,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1014万
-$21,890/呎
-(24年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+$1000万
+$21,598/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1058万
-$23,140/呎
-(22年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
+$1013万
+$22,166/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$567万
-$22,680/呎
-(24年-12月-03日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
+$559万
+$22,344/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$742万
-$22,960/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
+$731万
+$22,619/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45316,38 +45600,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$680万
-$27,076/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
+$572万
+$22,773/呎
+(26年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1183万
-$25,778/呎
+$1131万
+$24,638/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1204万
-$24,733/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45355,39 +45639,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
+$997万
+$21,542/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
 $1010万
-$21,825/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1025万
-$22,433/呎
-(24年-10月-30日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
+$22,101/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$565万
-$22,612/呎
-(26年-03月-15日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
+$556万
+$22,232/呎
+(24年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$739万
-$22,892/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+$721万
+$22,325/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45395,38 +45679,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I27" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$678万
-$26,992/呎
+$648万
+$25,801/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1180万
-$25,699/呎
+$1128万
+$24,564/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1201万
-$24,661/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45434,39 +45718,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1008万
-$21,760/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+$981万
+$21,184/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1022万
-$22,368/呎
-(24年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
+$995万
+$21,775/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$564万
-$22,544/呎
-(26年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
+$563万
+$22,524/呎
+(22年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$758万
-$23,471/呎
-(22年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+$710万
+$21,997/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45474,30 +45758,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$665万
-$26,510/呎
+$646万
+$25,725/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1158万
-$25,240/呎
+$1124万
+$24,490/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -45505,7 +45789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45513,328 +45797,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1004万
-$21,685/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1016万
-$22,234/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$560万
-$22,412/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$733万
-$22,687/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$652万
-$25,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$998万
-$21,747/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1000万
-$21,598/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1013万
-$22,166/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$559万
-$22,344/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$731万
-$22,619/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$650万
-$25,876/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1131万
-$24,638/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$997万
-$21,542/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1010万
-$22,101/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$556万
-$22,232/呎
-(24年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$721万
-$22,325/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$648万
-$25,801/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1128万
-$24,564/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$981万
-$21,184/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$995万
-$21,775/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$563万
-$22,524/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$710万
-$21,997/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$646万
-$25,725/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1124万
-$24,490/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
 $942万
 $20,339/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -45842,7 +45810,7 @@
           <t>D | 457呎 (2房)
 $961万
 $21,037/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -45850,7 +45818,7 @@
           <t>E | 250呎 (开放式)
 $524万
 $20,968/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -45964,17 +45932,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>202</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46072,7 +46040,7 @@
           <t>C | 443呎 (2房)
 $1111万
 $25,079/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -46088,7 +46056,7 @@
           <t>E | 325呎 (1房)
 $769万
 $23,649/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -46096,7 +46064,7 @@
           <t>F | 461呎 (2房)
 $1090万
 $23,644/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -46104,7 +46072,7 @@
           <t>G | 450呎 (2房)
 $1079万
 $23,987/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -46112,7 +46080,7 @@
           <t>H | 315呎 (1房)
 $754万
 $23,946/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -46120,7 +46088,7 @@
           <t>J | 316呎 (1房)
 $812万
 $25,693/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -46159,7 +46127,7 @@
           <t>C | 443呎 (2房)
 $1108万
 $25,002/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -46175,7 +46143,7 @@
           <t>E | 325呎 (1房)
 $766万
 $23,582/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -46183,7 +46151,7 @@
           <t>F | 461呎 (2房)
 $1087万
 $23,588/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -46191,7 +46159,7 @@
           <t>G | 450呎 (2房)
 $1077万
 $23,929/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -46199,7 +46167,7 @@
           <t>H | 315呎 (1房)
 $752万
 $23,876/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -46207,15 +46175,15 @@
           <t>J | 316呎 (1房)
 $810万
 $25,620/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="K6" s="24" t="inlineStr">
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $967万
 $29,401/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46238,7 +46206,7 @@
           <t>B | 467呎 (2房)
 $1183万
 $25,336/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -46246,7 +46214,7 @@
           <t>C | 443呎 (2房)
 $1104万
 $24,928/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -46262,7 +46230,7 @@
           <t>E | 325呎 (1房)
 $764万
 $23,511/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -46270,7 +46238,7 @@
           <t>F | 461呎 (2房)
 $1085万
 $23,544/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -46278,7 +46246,7 @@
           <t>G | 450呎 (2房)
 $1075万
 $23,887/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -46286,7 +46254,7 @@
           <t>H | 315呎 (1房)
 $750万
 $23,803/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -46294,15 +46262,15 @@
           <t>J | 316呎 (1房)
 $807万
 $25,541/呎
-(26年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="K7" s="24" t="inlineStr">
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $964万
 $29,313/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46325,7 +46293,7 @@
           <t>B | 467呎 (2房)
 $1176万
 $25,186/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -46333,7 +46301,7 @@
           <t>C | 443呎 (2房)
 $1098万
 $24,779/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -46349,7 +46317,7 @@
           <t>E | 325呎 (1房)
 $760万
 $23,372/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -46357,7 +46325,7 @@
           <t>F | 461呎 (2房)
 $1081万
 $23,443/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -46365,7 +46333,7 @@
           <t>G | 450呎 (2房)
 $1070万
 $23,782/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -46373,7 +46341,7 @@
           <t>H | 315呎 (1房)
 $745万
 $23,660/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -46381,15 +46349,15 @@
           <t>J | 316呎 (1房)
 $802万
 $25,389/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="K8" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $959万
 $29,137/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46412,7 +46380,7 @@
           <t>B | 467呎 (2房)
 $1173万
 $25,109/呎
-(24年-08月-19日)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -46420,15 +46388,15 @@
           <t>C | 443呎 (2房)
 $1094万
 $24,704/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $860万
 $27,114/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -46436,7 +46404,7 @@
           <t>E | 325呎 (1房)
 $757万
 $23,302/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -46444,7 +46412,7 @@
           <t>F | 461呎 (2房)
 $1078万
 $23,386/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -46452,7 +46420,7 @@
           <t>G | 450呎 (2房)
 $1064万
 $23,649/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -46460,7 +46428,7 @@
           <t>H | 315呎 (1房)
 $743万
 $23,590/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -46468,15 +46436,15 @@
           <t>J | 316呎 (1房)
 $800万
 $25,313/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="K9" s="24" t="inlineStr">
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $956万
 $29,049/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46491,7 +46459,7 @@
           <t>A | 620呎 (3房)
 $1590万
 $25,637/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -46499,7 +46467,7 @@
           <t>B | 467呎 (2房)
 $1169万
 $25,034/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -46507,15 +46475,15 @@
           <t>C | 443呎 (2房)
 $1091万
 $24,632/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $857万
 $27,032/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -46523,7 +46491,7 @@
           <t>E | 325呎 (1房)
 $755万
 $23,231/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -46531,7 +46499,7 @@
           <t>F | 461呎 (2房)
 $1076万
 $23,330/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -46539,7 +46507,7 @@
           <t>G | 450呎 (2房)
 $1061万
 $23,578/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -46547,7 +46515,7 @@
           <t>H | 315呎 (1房)
 $741万
 $23,521/呎
-(26年-04月-06日)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -46555,15 +46523,15 @@
           <t>J | 316呎 (1房)
 $798万
 $25,237/呎
-(26年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr">
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $953万
 $28,964/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46573,12 +46541,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(已定价未售)</t>
+$1543万
+$24,892/呎
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -46586,7 +46554,7 @@
           <t>B | 467呎 (2房)
 $1166万
 $24,959/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -46594,15 +46562,15 @@
           <t>C | 443呎 (2房)
 $1088万
 $24,558/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $854万
 $26,950/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -46610,7 +46578,7 @@
           <t>E | 325呎 (1房)
 $753万
 $23,160/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -46618,7 +46586,7 @@
           <t>F | 461呎 (2房)
 $1073万
 $23,273/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -46626,7 +46594,7 @@
           <t>G | 450呎 (2房)
 $1058万
 $23,507/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -46634,7 +46602,7 @@
           <t>H | 315呎 (1房)
 $739万
 $23,451/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -46642,15 +46610,15 @@
           <t>J | 316呎 (1房)
 $795万
 $25,161/呎
-(24年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="K11" s="24" t="inlineStr">
+(24年-08月-02日)</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $950万
 $28,875/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46665,7 +46633,7 @@
           <t>A | 620呎 (3房)
 $1536万
 $24,781/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -46673,7 +46641,7 @@
           <t>B | 467呎 (2房)
 $1195万
 $25,593/呎
-(22年-09月-29日)</t>
+(22年-09月-30日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -46681,15 +46649,15 @@
           <t>C | 443呎 (2房)
 $1085万
 $24,483/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $852万
 $26,871/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -46697,7 +46665,7 @@
           <t>E | 325呎 (1房)
 $750万
 $23,092/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -46705,7 +46673,7 @@
           <t>F | 461呎 (2房)
 $1070万
 $23,219/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -46713,7 +46681,7 @@
           <t>G | 450呎 (2房)
 $1055万
 $23,436/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -46721,7 +46689,7 @@
           <t>H | 315呎 (1房)
 $736万
 $23,378/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -46729,15 +46697,15 @@
           <t>J | 316呎 (1房)
 $793万
 $25,089/呎
-(24年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr">
+(24年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $947万
 $28,790/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46752,7 +46720,7 @@
           <t>A | 620呎 (3房)
 $1532万
 $24,705/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -46760,7 +46728,7 @@
           <t>B | 468呎 (2房)
 $1192万
 $25,462/呎
-(22年-10月-05日)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -46768,15 +46736,15 @@
           <t>C | 443呎 (2房)
 $1081万
 $24,411/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $849万
 $26,789/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -46784,7 +46752,7 @@
           <t>E | 325呎 (1房)
 $748万
 $23,022/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -46792,7 +46760,7 @@
           <t>F | 461呎 (2房)
 $1068万
 $23,163/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -46800,7 +46768,7 @@
           <t>G | 450呎 (2房)
 $1052万
 $23,369/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -46808,7 +46776,7 @@
           <t>H | 315呎 (1房)
 $734万
 $23,308/呎
-(24年-07月-09日)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -46816,7 +46784,7 @@
           <t>J | 317呎 (1房)
 $813万
 $25,640/呎
-(22年-09月-27日)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -46824,7 +46792,7 @@
           <t>K | 329呎 (1房)
 $831万
 $25,261/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -46839,7 +46807,7 @@
           <t>A | 620呎 (3房)
 $1527万
 $24,631/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -46847,7 +46815,7 @@
           <t>B | 468呎 (2房)
 $1188万
 $25,385/呎
-(22年-11月-23日)</t>
+(22年-11月-24日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46855,7 +46823,7 @@
           <t>C | 443呎 (2房)
 $1078万
 $24,336/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -46871,7 +46839,7 @@
           <t>E | 325呎 (1房)
 $746万
 $22,954/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -46879,7 +46847,7 @@
           <t>F | 461呎 (2房)
 $1065万
 $23,106/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -46887,7 +46855,7 @@
           <t>G | 450呎 (2房)
 $1048万
 $23,298/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -46895,7 +46863,7 @@
           <t>H | 315呎 (1房)
 $732万
 $23,238/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -46903,7 +46871,7 @@
           <t>J | 317呎 (1房)
 $810万
 $25,565/呎
-(22年-09月-27日)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -46911,7 +46879,7 @@
           <t>K | 329呎 (1房)
 $829万
 $25,185/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -46921,12 +46889,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(已定价未售)</t>
+$1525万
+$24,595/呎
+(26年-07月-26日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -46934,7 +46902,7 @@
           <t>B | 467呎 (2房)
 $1152万
 $24,664/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -46942,7 +46910,7 @@
           <t>C | 443呎 (2房)
 $1075万
 $24,266/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -46958,7 +46926,7 @@
           <t>E | 325呎 (1房)
 $744万
 $22,883/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -46966,7 +46934,7 @@
           <t>F | 461呎 (2房)
 $1063万
 $23,052/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -46974,7 +46942,7 @@
           <t>G | 450呎 (2房)
 $1045万
 $23,227/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -46982,7 +46950,7 @@
           <t>H | 315呎 (1房)
 $730万
 $23,171/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -46990,7 +46958,7 @@
           <t>J | 317呎 (1房)
 $808万
 $25,486/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -46998,7 +46966,7 @@
           <t>K | 329呎 (1房)
 $836万
 $25,395/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -47013,7 +46981,7 @@
           <t>A | 620呎 (3房)
 $1518万
 $24,484/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -47021,7 +46989,7 @@
           <t>B | 468呎 (2房)
 $1148万
 $24,538/呎
-(23年-04月-12日)</t>
+(23年-04月-13日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -47029,7 +46997,7 @@
           <t>C | 443呎 (2房)
 $1072万
 $24,192/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -47045,7 +47013,7 @@
           <t>E | 325呎 (1房)
 $742万
 $22,815/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -47053,7 +47021,7 @@
           <t>F | 461呎 (2房)
 $1061万
 $23,020/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -47061,7 +47029,7 @@
           <t>G | 450呎 (2房)
 $1042万
 $23,158/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -47069,7 +47037,7 @@
           <t>H | 315呎 (1房)
 $728万
 $23,102/呎
-(24年-06月-12日)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -47077,7 +47045,7 @@
           <t>J | 317呎 (1房)
 $783万
 $24,710/呎
-(22年-09月-27日)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -47085,7 +47053,7 @@
           <t>K | 329呎 (1房)
 $847万
 $25,745/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -47095,12 +47063,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -47108,7 +47076,7 @@
           <t>B | 467呎 (2房)
 $1142万
 $24,443/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -47116,7 +47084,7 @@
           <t>C | 443呎 (2房)
 $1065万
 $24,047/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -47132,7 +47100,7 @@
           <t>E | 325呎 (1房)
 $737万
 $22,680/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -47140,7 +47108,7 @@
           <t>F | 461呎 (2房)
 $1056万
 $22,918/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -47148,7 +47116,7 @@
           <t>G | 450呎 (2房)
 $1036万
 $23,020/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -47156,7 +47124,7 @@
           <t>H | 315呎 (1房)
 $744万
 $23,616/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -47164,7 +47132,7 @@
           <t>J | 317呎 (1房)
 $779万
 $24,565/呎
-(23年-03月-22日)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -47172,7 +47140,7 @@
           <t>K | 329呎 (1房)
 $819万
 $24,884/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -47187,7 +47155,7 @@
           <t>A | 620呎 (3房)
 $1504万
 $24,266/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -47195,7 +47163,7 @@
           <t>B | 467呎 (2房)
 $1138万
 $24,370/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -47203,15 +47171,15 @@
           <t>C | 443呎 (2房)
 $1062万
 $23,975/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $834万
 $26,312/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -47219,7 +47187,7 @@
           <t>E | 325呎 (1房)
 $735万
 $22,612/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -47227,7 +47195,7 @@
           <t>F | 461呎 (2房)
 $1054万
 $22,863/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -47235,7 +47203,7 @@
           <t>G | 450呎 (2房)
 $1033万
 $22,951/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -47243,7 +47211,7 @@
           <t>H | 315呎 (1房)
 $742万
 $23,546/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -47251,7 +47219,7 @@
           <t>J | 316呎 (1房)
 $798万
 $25,266/呎
-(22年-09月-28日)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -47259,7 +47227,7 @@
           <t>K | 329呎 (1房)
 $840万
 $25,517/呎
-(22年-10月-11日)</t>
+(22年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -47269,12 +47237,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(已定价未售)</t>
+$1502万
+$24,229/呎
+(26年-07月-26日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -47282,7 +47250,7 @@
           <t>B | 467呎 (2房)
 $1135万
 $24,296/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47290,15 +47258,15 @@
           <t>C | 443呎 (2房)
 $1059万
 $23,905/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $832万
 $26,233/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -47306,7 +47274,7 @@
           <t>E | 325呎 (1房)
 $733万
 $22,545/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -47314,7 +47282,7 @@
           <t>F | 461呎 (2房)
 $1052万
 $22,809/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -47322,7 +47290,7 @@
           <t>G | 450呎 (2房)
 $1030万
 $22,882/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -47330,7 +47298,7 @@
           <t>H | 315呎 (1房)
 $719万
 $22,825/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -47338,7 +47306,7 @@
           <t>J | 316呎 (1房)
 $796万
 $25,190/呎
-(22年-09月-28日)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -47346,7 +47314,7 @@
           <t>K | 329呎 (1房)
 $814万
 $24,739/呎
-(22年-12月-01日)</t>
+(22年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -47361,7 +47329,7 @@
           <t>A | 620呎 (3房)
 $1496万
 $24,121/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -47369,7 +47337,7 @@
           <t>B | 467呎 (2房)
 $1163万
 $24,912/呎
-(22年-09月-29日)</t>
+(22年-09月-30日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -47377,15 +47345,15 @@
           <t>C | 443呎 (2房)
 $1056万
 $23,833/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $829万
 $26,155/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -47393,7 +47361,7 @@
           <t>E | 325呎 (1房)
 $730万
 $22,477/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -47401,7 +47369,7 @@
           <t>F | 461呎 (2房)
 $1036万
 $22,475/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -47409,7 +47377,7 @@
           <t>G | 450呎 (2房)
 $1027万
 $22,816/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -47417,7 +47385,7 @@
           <t>H | 315呎 (1房)
 $717万
 $22,759/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -47425,7 +47393,7 @@
           <t>J | 316呎 (1房)
 $794万
 $25,114/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -47433,7 +47401,7 @@
           <t>K | 329呎 (1房)
 $811万
 $24,663/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -47448,7 +47416,7 @@
           <t>A | 620呎 (3房)
 $1491万
 $24,048/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -47456,7 +47424,7 @@
           <t>B | 468呎 (2房)
 $1160万
 $24,784/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -47464,15 +47432,15 @@
           <t>C | 443呎 (2房)
 $1053万
 $23,761/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $827万
 $26,079/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -47480,7 +47448,7 @@
           <t>E | 325呎 (1房)
 $728万
 $22,409/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -47488,7 +47456,7 @@
           <t>F | 461呎 (2房)
 $1033万
 $22,408/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -47496,7 +47464,7 @@
           <t>G | 450呎 (2房)
 $1024万
 $22,747/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -47504,7 +47472,7 @@
           <t>H | 315呎 (1房)
 $715万
 $22,692/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -47512,7 +47480,7 @@
           <t>J | 317呎 (1房)
 $791万
 $24,959/呎
-(22年-09月-27日)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -47520,7 +47488,7 @@
           <t>K | 329呎 (1房)
 $809万
 $24,590/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -47535,7 +47503,7 @@
           <t>A | 620呎 (3房)
 $1486万
 $23,976/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -47543,7 +47511,7 @@
           <t>B | 467呎 (2房)
 $1124万
 $24,079/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47551,15 +47519,15 @@
           <t>C | 443呎 (2房)
 $1049万
 $23,688/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $824万
 $26,000/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -47567,7 +47535,7 @@
           <t>E | 325呎 (1房)
 $726万
 $22,342/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -47575,7 +47543,7 @@
           <t>F | 461呎 (2房)
 $1030万
 $22,341/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -47583,7 +47551,7 @@
           <t>G | 450呎 (2房)
 $1020万
 $22,678/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -47591,7 +47559,7 @@
           <t>H | 315呎 (1房)
 $733万
 $23,263/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -47599,7 +47567,7 @@
           <t>J | 316呎 (1房)
 $767万
 $24,275/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -47607,7 +47575,7 @@
           <t>K | 329呎 (1房)
 $807万
 $24,517/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -47622,7 +47590,7 @@
           <t>A | 620呎 (3房)
 $1482万
 $23,905/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -47630,7 +47598,7 @@
           <t>B | 467呎 (2房)
 $1153万
 $24,690/呎
-(22年-10月-10日)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47638,7 +47606,7 @@
           <t>C | 443呎 (2房)
 $1046万
 $23,621/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -47654,7 +47622,7 @@
           <t>E | 325呎 (1房)
 $724万
 $22,277/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -47662,7 +47630,7 @@
           <t>F | 461呎 (2房)
 $1027万
 $22,273/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -47670,7 +47638,7 @@
           <t>G | 450呎 (2房)
 $1017万
 $22,609/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -47678,7 +47646,7 @@
           <t>H | 315呎 (1房)
 $710万
 $22,556/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -47686,7 +47654,7 @@
           <t>J | 316呎 (1房)
 $765万
 $24,203/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -47694,7 +47662,7 @@
           <t>K | 329呎 (1房)
 $804万
 $24,444/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -47709,7 +47677,7 @@
           <t>A | 620呎 (3房)
 $1478万
 $23,834/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -47717,7 +47685,7 @@
           <t>B | 467呎 (2房)
 $1150万
 $24,617/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47725,7 +47693,7 @@
           <t>C | 443呎 (2房)
 $1043万
 $23,549/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -47741,7 +47709,7 @@
           <t>E | 325呎 (1房)
 $722万
 $22,209/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -47749,7 +47717,7 @@
           <t>F | 461呎 (2房)
 $1024万
 $22,208/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -47757,7 +47725,7 @@
           <t>G | 450呎 (2房)
 $1014万
 $22,542/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -47765,7 +47733,7 @@
           <t>H | 315呎 (1房)
 $728万
 $23,127/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -47773,7 +47741,7 @@
           <t>J | 317呎 (1房)
 $784万
 $24,735/呎
-(22年-10月-09日)</t>
+(22年-10月-10日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -47781,7 +47749,7 @@
           <t>K | 329呎 (1房)
 $802万
 $24,368/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -47796,7 +47764,7 @@
           <t>A | 620呎 (3房)
 $1469万
 $23,692/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -47804,7 +47772,7 @@
           <t>B | 468呎 (2房)
 $1111万
 $23,741/呎
-(22年-10月-06日)</t>
+(22年-10月-07日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47812,7 +47780,7 @@
           <t>C | 443呎 (2房)
 $1037万
 $23,409/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -47828,7 +47796,7 @@
           <t>E | 325呎 (1房)
 $718万
 $22,077/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -47836,7 +47804,7 @@
           <t>F | 461呎 (2房)
 $1018万
 $22,076/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -47844,7 +47812,7 @@
           <t>G | 450呎 (2房)
 $1008万
 $22,409/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -47852,7 +47820,7 @@
           <t>H | 315呎 (1房)
 $704万
 $22,352/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -47860,7 +47828,7 @@
           <t>J | 316呎 (1房)
 $758万
 $23,984/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -47868,7 +47836,7 @@
           <t>K | 329呎 (1房)
 $797万
 $24,225/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -47891,7 +47859,7 @@
           <t>B | 467呎 (2房)
 $1108万
 $23,722/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47899,7 +47867,7 @@
           <t>C | 443呎 (2房)
 $1034万
 $23,339/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -47915,7 +47883,7 @@
           <t>E | 325呎 (1房)
 $717万
 $22,068/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -47923,7 +47891,7 @@
           <t>F | 461呎 (2房)
 $1015万
 $22,009/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -47931,7 +47899,7 @@
           <t>G | 450呎 (2房)
 $1005万
 $22,342/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -47939,7 +47907,7 @@
           <t>H | 315呎 (1房)
 $704万
 $22,340/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -47947,15 +47915,15 @@
           <t>J | 316呎 (1房)
 $756万
 $23,915/呎
-(24年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr">
+(24年-05月-30日)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
-$903万
-$27,444/呎
-(已定价未售)</t>
+$795万
+$24,152/呎
+(26年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -47978,7 +47946,7 @@
           <t>B | 467呎 (2房)
 $1104万
 $23,649/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47986,7 +47954,7 @@
           <t>C | 443呎 (2房)
 $1031万
 $23,269/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -48002,7 +47970,7 @@
           <t>E | 325呎 (1房)
 $715万
 $21,994/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -48010,7 +47978,7 @@
           <t>F | 461呎 (2房)
 $1012万
 $21,944/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -48018,7 +47986,7 @@
           <t>G | 450呎 (2房)
 $1002万
 $22,276/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -48026,7 +47994,7 @@
           <t>H | 315呎 (1房)
 $701万
 $22,267/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -48034,15 +48002,15 @@
           <t>J | 316呎 (1房)
 $753万
 $23,842/呎
-(24年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
+(24年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $900万
 $27,362/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -48065,7 +48033,7 @@
           <t>B | 467呎 (2房)
 $1101万
 $23,580/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -48073,7 +48041,7 @@
           <t>C | 443呎 (2房)
 $1028万
 $23,199/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -48089,7 +48057,7 @@
           <t>E | 325呎 (1房)
 $707万
 $21,760/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -48097,7 +48065,7 @@
           <t>F | 461呎 (2房)
 $1002万
 $21,727/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -48105,7 +48073,7 @@
           <t>G | 450呎 (2房)
 $992万
 $22,053/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -48113,7 +48081,7 @@
           <t>H | 315呎 (1房)
 $691万
 $21,924/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -48121,15 +48089,15 @@
           <t>J | 316呎 (1房)
 $751万
 $23,769/呎
-(24年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
+(24年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $898万
 $27,280/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -48152,7 +48120,7 @@
           <t>B | 429呎 (2房)
 $1108万
 $25,828/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -48160,7 +48128,7 @@
           <t>C | 406呎 (2房)
 $999万
 $24,606/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -48176,7 +48144,7 @@
           <t>E | 325呎 (1房)
 $681万
 $20,963/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -48184,7 +48152,7 @@
           <t>F | 461呎 (2房)
 $972万
 $21,093/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -48192,7 +48160,7 @@
           <t>G | 450呎 (2房)
 $964万
 $21,411/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -48200,7 +48168,7 @@
           <t>H | 315呎 (1房)
 $681万
 $21,616/呎
-(22年-09月-28日)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -48208,15 +48176,15 @@
           <t>J | 316呎 (1房)
 $749万
 $23,699/呎
-(24年-11月-04日)</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $895万
 $27,198/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
         <v>10483000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>23400</v>
+        <v>23347</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>10483000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>23400</v>
+        <v>23347</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -5232,38 +5232,30 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>10452000</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>23330</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K72" s="5" t="n">
+        <v>10452000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>23330</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5272,7 +5264,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7482,38 +7474,30 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>10266000</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>22915</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K107" s="5" t="n">
+        <v>10266000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>22915</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7522,7 +7506,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16858,34 +16842,34 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>8683000</v>
+        <v>7642000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>26882</v>
+        <v>23659</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>7641040</v>
+        <v>7642000</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>23656</v>
+        <v>23659</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -17440,34 +17424,34 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
-        <v>8657000</v>
+        <v>7619000</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>26802</v>
+        <v>23588</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K260" s="5" t="n">
-        <v>7618160</v>
+        <v>7619000</v>
       </c>
       <c r="L260" s="5" t="n">
-        <v>23586</v>
+        <v>23588</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -19162,34 +19146,34 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
-        <v>8554000</v>
+        <v>7528000</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>26483</v>
+        <v>23307</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K287" s="5" t="n">
-        <v>7527520</v>
+        <v>7528000</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>23305</v>
+        <v>23307</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -37462,34 +37446,34 @@
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H577" s="5" t="n">
-        <v>8242000</v>
+        <v>7253000</v>
       </c>
       <c r="I577" s="5" t="n">
-        <v>26000</v>
+        <v>22880</v>
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>7252960</v>
+        <v>7253000</v>
       </c>
       <c r="L577" s="5" t="n">
         <v>22880</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -42099,7 +42083,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42109,7 +42093,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42766,10 +42750,10 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 448呎 (2房)
+          <t>F | 449呎 (2房)
 $1048万
-$23,400/呎
-(26年-07月-14日)</t>
+$23,347/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -42827,7 +42811,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$1045万
+$23,330/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1242万
+$24,890/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1828万
+$25,535/呎
+(22年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1668万
+$25,234/呎
+(24年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 486呎 (2房)
+$1243万
+$25,570/呎
+(22年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$709万
+$22,299/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42835,54 +42882,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 499呎 (2房)
-$1242万
-$24,890/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1238万
+$24,816/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 716呎 (3房)
-$1828万
-$25,535/呎
-(22年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+$1817万
+$25,383/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 661呎 (3房)
-$1668万
-$25,234/呎
-(24年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 486呎 (2房)
-$1243万
-$25,570/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+$1658万
+$25,085/呎
+(24年-06月-06日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1235万
+$25,470/呎
+(25年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 318呎 (1房)
-$709万
-$22,299/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$705万
+$22,164/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42890,7 +42937,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42898,54 +42945,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 499呎 (2房)
-$1238万
-$24,816/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+$1231万
+$24,667/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 716呎 (3房)
-$1817万
-$25,383/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
+$1812万
+$25,307/呎
+(24年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 661呎 (3房)
-$1658万
-$25,085/呎
-(24年-06月-06日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+$1653万
+$25,008/呎
+(25年-03月-05日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 485呎 (2房)
-$1235万
-$25,470/呎
-(25年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+$1232万
+$25,394/呎
+(24年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 318呎 (1房)
-$705万
-$22,164/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$723万
+$22,726/呎
+(22年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42953,7 +43000,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42961,54 +43008,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 499呎 (2房)
-$1231万
-$24,667/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1227万
+$24,593/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 716呎 (3房)
-$1812万
-$25,307/呎
-(24年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+$1807万
+$25,232/呎
+(24年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 661呎 (3房)
-$1653万
-$25,008/呎
-(25年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+$1648万
+$24,933/呎
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 485呎 (2房)
-$1232万
-$25,394/呎
-(24年-10月-30日)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
+$1228万
+$25,318/呎
+(25年-01月-06日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 318呎 (1房)
-$723万
-$22,726/呎
-(22年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$701万
+$22,031/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43016,7 +43063,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43024,54 +43071,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 499呎 (2房)
-$1227万
-$24,593/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$1224万
+$24,521/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 716呎 (3房)
-$1807万
-$25,232/呎
-(24年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
+$1801万
+$25,155/呎
+(24年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 661呎 (3房)
-$1648万
-$24,933/呎
-(25年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
+$1643万
+$24,859/呎
+(24年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 485呎 (2房)
-$1228万
-$25,318/呎
-(25年-01月-06日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+$1224万
+$25,243/呎
+(24年-10月-29日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 318呎 (1房)
-$701万
-$22,031/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$698万
+$21,965/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43079,75 +43126,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1224万
-$24,521/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1801万
-$25,155/呎
-(24年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1643万
-$24,859/呎
-(24年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1224万
-$25,243/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$698万
-$21,965/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-招标单位
--
-(在售)</t>
+$1027万
+$22,915/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -43803,7 +43787,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43813,7 +43797,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44557,12 +44541,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$868万
-$26,882/呎
-(在售)</t>
+$764万
+$23,659/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -44636,12 +44620,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$866万
-$26,802/呎
-(在售)</t>
+$762万
+$23,588/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -44873,12 +44857,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$855万
-$26,483/呎
-(在售)</t>
+$753万
+$23,307/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -45932,7 +45916,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45942,7 +45926,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47522,12 +47506,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
-$824万
-$26,000/呎
-(在售)</t>
+$725万
+$22,880/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -23611,7 +23611,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -35777,7 +35777,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -45510,7 +45510,7 @@
           <t>H | 251呎 (开放式)
 $573万
 $22,845/呎
-(26年-07月-28日)</t>
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -47226,7 +47226,7 @@
           <t>A | 620呎 (3房)
 $1502万
 $24,229/呎
-(26年-07月-26日)</t>
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -40174,34 +40174,34 @@
       </c>
       <c r="F621" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H621" s="5" t="n">
-        <v>9002000</v>
+        <v>7922000</v>
       </c>
       <c r="I621" s="5" t="n">
-        <v>27362</v>
+        <v>24079</v>
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K621" s="5" t="n">
-        <v>7921760</v>
+        <v>7922000</v>
       </c>
       <c r="L621" s="5" t="n">
-        <v>24078</v>
+        <v>24079</v>
       </c>
       <c r="M621" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N621" s="3" t="inlineStr">
@@ -44704,7 +44704,7 @@
           <t>F | 323呎 (1房)
 $760万
 $23,517/呎
-(26年-07月-26日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -45589,7 +45589,7 @@
           <t>H | 251呎 (开放式)
 $572万
 $22,773/呎
-(26年-07月-26日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -45916,7 +45916,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46878,7 +46878,7 @@
           <t>A | 620呎 (3房)
 $1525万
 $24,595/呎
-(26年-07月-26日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -47989,12 +47989,12 @@
 (24年-05月-27日)</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
-$900万
-$27,362/呎
-(在售)</t>
+$792万
+$24,079/呎
+(26年-08月-16日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -7024,38 +7024,30 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>10297000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>22984</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K100" s="5" t="n">
+        <v>10297000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>22984</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7064,7 +7056,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12898,38 +12890,30 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I191" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>10755000</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>23229</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K191" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L191" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K191" s="5" t="n">
+        <v>10755000</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>23229</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12938,7 +12922,7 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15980,38 +15964,30 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>12615000</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>25903</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" s="5" t="n">
+        <v>12615000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>25903</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -16020,7 +15996,7 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16252,34 +16228,34 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>8709000</v>
+        <v>7664000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>26963</v>
+        <v>23728</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>7663920</v>
+        <v>7664000</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>23727</v>
+        <v>23728</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -17160,38 +17136,30 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>12536000</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>25741</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K256" s="5" t="n">
+        <v>12536000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>25741</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -17200,7 +17168,7 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19588,34 +19556,34 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
-        <v>6878000</v>
+        <v>6053000</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>27402</v>
+        <v>24116</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>6052640</v>
+        <v>6053000</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>24114</v>
+        <v>24116</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -30809,7 +30777,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -34524,38 +34492,30 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H530" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I530" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H530" s="5" t="n">
+        <v>15112000</v>
+      </c>
+      <c r="I530" s="5" t="n">
+        <v>24374</v>
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K530" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L530" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K530" s="5" t="n">
+        <v>15112000</v>
+      </c>
+      <c r="L530" s="5" t="n">
+        <v>24374</v>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
@@ -34564,7 +34524,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39559,7 +39519,7 @@
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H611" s="5" t="n">
@@ -42083,7 +42043,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42093,7 +42053,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43063,12 +43023,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-招标单位
--
-(在售)</t>
+$1030万
+$22,984/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -43787,7 +43747,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43797,7 +43757,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43964,7 +43924,165 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1076万
+$23,229/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1087万
+$23,783/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$680万
+$27,196/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$889万
+$27,533/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$717万
+$28,574/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1068万
+$23,076/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1085万
+$23,740/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$678万
+$27,116/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$887万
+$27,452/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$715万
+$28,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1264万
+$25,947/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
 招标单位
@@ -43972,31 +44090,31 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1087万
-$23,783/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
+$1080万
+$23,637/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$680万
-$27,196/呎
+$674万
+$26,956/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$889万
-$27,533/呎
+$881万
+$27,288/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44004,15 +44122,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$717万
-$28,574/呎
+$711万
+$28,319/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44021,13 +44139,250 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1260万
+$25,871/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1078万
+$23,580/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$672万
+$26,872/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$879万
+$27,207/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$709万
+$28,235/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1256万
+$25,793/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1054万
+$22,760/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1069万
+$23,396/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$590万
+$23,580/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$876万
+$27,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$706万
+$28,147/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1262万
+$25,903/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1051万
+$22,691/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1066万
+$23,324/呎
+(24年-10月-29日)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,508/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$874万
+$27,043/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$704万
+$28,064/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -44035,7 +44390,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44043,39 +44398,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1068万
-$23,076/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
+$1047万
+$22,622/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1085万
-$23,740/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
+$1063万
+$23,254/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$678万
-$27,116/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
+$586万
+$23,440/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$887万
-$27,452/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
+$766万
+$23,728/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44083,15 +44438,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$715万
-$28,490/呎
+$702万
+$27,980/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44100,21 +44455,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1264万
-$25,947/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+$1254万
+$25,741/呎
+(26年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44122,39 +44477,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
+$1044万
+$22,555/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1080万
-$23,637/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
+$1060万
+$23,186/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$674万
-$26,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
+$584万
+$23,368/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$881万
-$27,288/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
+$764万
+$23,659/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44162,15 +44517,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I13" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$711万
-$28,319/呎
+$700万
+$27,896/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44179,21 +44534,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1260万
-$25,871/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+$1242万
+$25,503/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44201,39 +44556,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
+$1041万
+$22,488/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1078万
-$23,580/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
+$1056万
+$23,116/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$672万
-$26,872/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
+$582万
+$23,296/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$879万
-$27,207/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
+$762万
+$23,588/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44241,38 +44596,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$709万
-$28,235/呎
+$698万
+$27,813/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+$1070万
+$23,305/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1256万
-$25,793/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+$1237万
+$25,409/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44280,39 +44635,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1054万
-$22,760/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
+$1038万
+$22,421/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1069万
-$23,396/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
+$1053万
+$23,046/呎
+(24年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$590万
-$23,580/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
+$581万
+$23,232/呎
+(24年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$876万
-$27,124/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+$760万
+$23,517/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44320,38 +44675,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$706万
-$28,147/呎
+$696万
+$27,729/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+$1066万
+$23,235/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+$1234万
+$25,333/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44359,39 +44714,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1051万
-$22,691/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
+$1035万
+$22,354/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1066万
-$23,324/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
+$1050万
+$22,978/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$588万
-$23,508/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
+$579万
+$23,160/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$874万
-$27,043/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
+$860万
+$26,641/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44399,38 +44754,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$704万
-$28,064/呎
+$694万
+$27,649/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
+$1063万
+$23,166/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+$1226万
+$25,181/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44438,39 +44793,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1047万
-$22,622/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+$1029万
+$22,222/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1063万
-$23,254/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
+$1044万
+$22,840/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$586万
-$23,440/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
+$576万
+$23,024/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$871万
-$26,963/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
+$753万
+$23,307/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44478,38 +44833,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$702万
-$27,980/呎
+$690万
+$27,482/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
+$1201万
+$26,166/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+$1236万
+$25,382/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44517,39 +44872,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1044万
-$22,555/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
+$1026万
+$22,156/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1060万
-$23,186/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
+$1041万
+$22,772/呎
+(24年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$584万
-$23,368/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
+$574万
+$22,952/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$764万
-$23,659/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$772万
+$23,895/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44557,407 +44912,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$700万
-$27,896/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1242万
-$25,503/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1041万
-$22,488/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1056万
-$23,116/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$582万
-$23,296/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$762万
-$23,588/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$698万
-$27,813/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1070万
-$23,305/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1237万
-$25,409/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1038万
-$22,421/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1053万
-$23,046/呎
-(24年-10月-31日)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$581万
-$23,232/呎
-(24年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$760万
-$23,517/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$696万
-$27,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1066万
-$23,235/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1234万
-$25,333/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1035万
-$22,354/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1050万
-$22,978/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$579万
-$23,160/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$860万
-$26,641/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$694万
-$27,649/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1063万
-$23,166/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1226万
-$25,181/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1029万
-$22,222/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1044万
-$22,840/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$576万
-$23,024/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$753万
-$23,307/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$690万
-$27,482/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1201万
-$26,166/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1236万
-$25,382/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1026万
-$22,156/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1041万
-$22,772/呎
-(24年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$574万
-$22,952/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$772万
-$23,895/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$688万
-$27,402/呎
-(在售)</t>
+$605万
+$24,116/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -45916,7 +45876,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45926,7 +45886,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46530,7 +46490,7 @@
           <t>A | 620呎 (3房)
 $1543万
 $24,892/呎
-(26年-07月-27日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -47047,12 +47007,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1511万
+$24,374/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -47907,7 +47867,7 @@
           <t>K | 329呎 (1房)
 $795万
 $24,152/呎
-(26年-07月-26日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -13022,38 +13022,30 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>12835000</v>
+      </c>
+      <c r="I193" s="5" t="n">
+        <v>26355</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K193" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L193" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K193" s="5" t="n">
+        <v>12835000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>26355</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -13062,7 +13054,7 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21733,7 +21725,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21852,34 +21844,34 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
-        <v>6796000</v>
+        <v>5981000</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>27076</v>
+        <v>23829</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>5980480</v>
+        <v>5981000</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>23827</v>
+        <v>23829</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -27640,7 +27632,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -27650,12 +27642,12 @@
       </c>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J420" s="3" t="inlineStr">
@@ -27665,12 +27657,12 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M420" s="3" t="inlineStr">
@@ -27680,7 +27672,7 @@
       </c>
       <c r="N420" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28268,7 +28260,7 @@
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -28278,12 +28270,12 @@
       </c>
       <c r="H430" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I430" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J430" s="3" t="inlineStr">
@@ -28293,12 +28285,12 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M430" s="3" t="inlineStr">
@@ -28308,7 +28300,7 @@
       </c>
       <c r="N430" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28896,7 +28888,7 @@
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -28906,12 +28898,12 @@
       </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I440" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J440" s="3" t="inlineStr">
@@ -28921,12 +28913,12 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M440" s="3" t="inlineStr">
@@ -28936,7 +28928,7 @@
       </c>
       <c r="N440" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29516,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -29534,12 +29526,12 @@
       </c>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I450" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J450" s="3" t="inlineStr">
@@ -29549,12 +29541,12 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M450" s="3" t="inlineStr">
@@ -29564,7 +29556,7 @@
       </c>
       <c r="N450" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34926,34 +34918,34 @@
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
-        <v>8341000</v>
+        <v>7341000</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>26312</v>
+        <v>23158</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K537" s="5" t="n">
-        <v>7340080</v>
+        <v>7341000</v>
       </c>
       <c r="L537" s="5" t="n">
-        <v>23155</v>
+        <v>23158</v>
       </c>
       <c r="M537" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N537" s="3" t="inlineStr">
@@ -40072,7 +40064,7 @@
       </c>
       <c r="F620" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G620" s="3" t="inlineStr">
@@ -40080,31 +40072,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H620" s="5" t="n">
-        <v>16641000</v>
-      </c>
-      <c r="I620" s="5" t="n">
-        <v>26840</v>
+      <c r="H620" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I620" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J620" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K620" s="5" t="n">
-        <v>14644080</v>
-      </c>
-      <c r="L620" s="5" t="n">
-        <v>23619</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K620" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L620" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M620" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N620" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
@@ -40700,31 +40700,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H630" s="5" t="n">
-        <v>16591000</v>
-      </c>
-      <c r="I630" s="5" t="n">
-        <v>26760</v>
+      <c r="H630" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I630" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K630" s="5" t="n">
-        <v>14600080</v>
-      </c>
-      <c r="L630" s="5" t="n">
-        <v>23549</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K630" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L630" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M630" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41312,7 +41320,7 @@
       </c>
       <c r="F640" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G640" s="3" t="inlineStr">
@@ -41320,31 +41328,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H640" s="5" t="n">
-        <v>16542000</v>
-      </c>
-      <c r="I640" s="5" t="n">
-        <v>26681</v>
+      <c r="H640" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I640" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J640" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K640" s="5" t="n">
-        <v>14556960</v>
-      </c>
-      <c r="L640" s="5" t="n">
-        <v>23479</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K640" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L640" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M640" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N640" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41932,7 +41948,7 @@
       </c>
       <c r="F650" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G650" s="3" t="inlineStr">
@@ -41940,31 +41956,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H650" s="5" t="n">
-        <v>16492000</v>
-      </c>
-      <c r="I650" s="5" t="n">
-        <v>26600</v>
+      <c r="H650" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I650" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J650" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K650" s="5" t="n">
-        <v>14512960</v>
-      </c>
-      <c r="L650" s="5" t="n">
-        <v>23408</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K650" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L650" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M650" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N650" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43771,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43757,7 +43781,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43908,7 +43932,86 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1284万
+$26,355/呎
+(26年-08月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1076万
+$23,229/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1087万
+$23,783/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$680万
+$27,196/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$889万
+$27,533/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$717万
+$28,574/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -43916,7 +44019,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -43924,39 +44027,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1076万
-$23,229/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
+$1068万
+$23,076/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1087万
-$23,783/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
+$1085万
+$23,740/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$680万
-$27,196/呎
+$678万
+$27,116/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$889万
-$27,533/呎
+$887万
+$27,452/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -43964,15 +44067,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$717万
-$28,574/呎
+$715万
+$28,490/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -43981,13 +44084,329 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1264万
+$25,947/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1080万
+$23,637/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$674万
+$26,956/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$881万
+$27,288/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$711万
+$28,319/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1260万
+$25,871/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1078万
+$23,580/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$672万
+$26,872/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$879万
+$27,207/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$709万
+$28,235/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1256万
+$25,793/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1054万
+$22,760/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1069万
+$23,396/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$590万
+$23,580/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$876万
+$27,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$706万
+$28,147/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1262万
+$25,903/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1051万
+$22,691/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1066万
+$23,324/呎
+(24年-10月-29日)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,508/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$874万
+$27,043/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$704万
+$28,064/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -43995,7 +44414,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44003,39 +44422,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1068万
-$23,076/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
+$1047万
+$22,622/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1085万
-$23,740/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
+$1063万
+$23,254/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$678万
-$27,116/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
+$586万
+$23,440/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$887万
-$27,452/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
+$766万
+$23,728/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44043,15 +44462,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$715万
-$28,490/呎
+$702万
+$27,980/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44060,21 +44479,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1264万
-$25,947/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+$1254万
+$25,741/呎
+(26年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44082,39 +44501,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
+$1044万
+$22,555/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1080万
-$23,637/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
+$1060万
+$23,186/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$674万
-$26,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
+$584万
+$23,368/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$881万
-$27,288/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
+$764万
+$23,659/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44122,15 +44541,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I13" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$711万
-$28,319/呎
+$700万
+$27,896/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44139,21 +44558,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1260万
-$25,871/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+$1242万
+$25,503/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44161,39 +44580,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
+$1041万
+$22,488/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1078万
-$23,580/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
+$1056万
+$23,116/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$672万
-$26,872/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
+$582万
+$23,296/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$879万
-$27,207/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
+$762万
+$23,588/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44201,38 +44620,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$709万
-$28,235/呎
+$698万
+$27,813/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+$1070万
+$23,305/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1256万
-$25,793/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+$1237万
+$25,409/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44240,39 +44659,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1054万
-$22,760/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
+$1038万
+$22,421/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1069万
-$23,396/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
+$1053万
+$23,046/呎
+(24年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$590万
-$23,580/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
+$581万
+$23,232/呎
+(24年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$876万
-$27,124/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+$760万
+$23,517/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44280,38 +44699,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$706万
-$28,147/呎
+$696万
+$27,729/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+$1066万
+$23,235/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1262万
-$25,903/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+$1234万
+$25,333/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44319,39 +44738,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1051万
-$22,691/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
+$1035万
+$22,354/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1066万
-$23,324/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
+$1050万
+$22,978/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$588万
-$23,508/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
+$579万
+$23,160/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$874万
-$27,043/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
+$860万
+$26,641/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44359,38 +44778,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$704万
-$28,064/呎
+$694万
+$27,649/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
+$1063万
+$23,166/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+$1226万
+$25,181/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44398,39 +44817,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1047万
-$22,622/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+$1029万
+$22,222/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1063万
-$23,254/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
+$1044万
+$22,840/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$586万
-$23,440/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
+$576万
+$23,024/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$766万
-$23,728/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
+$753万
+$23,307/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44438,38 +44857,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$702万
-$27,980/呎
+$690万
+$27,482/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
+$1201万
+$26,166/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1254万
-$25,741/呎
-(26年-08月-21日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+$1236万
+$25,382/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44477,39 +44896,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1044万
-$22,555/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
+$1026万
+$22,156/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1060万
-$23,186/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
+$1041万
+$22,772/呎
+(24年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$584万
-$23,368/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
+$574万
+$22,952/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$764万
-$23,659/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$772万
+$23,895/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44517,38 +44936,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$700万
-$27,896/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
+$605万
+$24,116/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+$1054万
+$22,959/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1242万
-$25,503/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+$1233万
+$25,322/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44556,39 +44975,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1041万
-$22,488/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
+$1023万
+$22,089/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1056万
-$23,116/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
+$1038万
+$22,705/呎
+(24年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$582万
-$23,296/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
+$588万
+$23,536/呎
+(22年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$762万
-$23,588/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+$748万
+$23,167/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44596,38 +45015,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$698万
-$27,813/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
+$686万
+$27,319/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1070万
-$23,305/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+$1080万
+$23,540/呎
+(22年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1237万
-$25,409/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+$1230万
+$25,261/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44635,39 +45054,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1038万
-$22,421/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+$1020万
+$22,022/呎
+(24年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1053万
-$23,046/呎
-(24年-10月-31日)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
+$1064万
+$23,280/呎
+(22年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$581万
-$23,232/呎
-(24年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
+$587万
+$23,464/呎
+(22年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$760万
-$23,517/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+$746万
+$23,096/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44675,38 +45094,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$696万
-$27,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
+$684万
+$27,239/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1066万
-$23,235/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1048万
+$22,821/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1234万
-$25,333/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+$1227万
+$25,201/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44714,39 +45133,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1035万
-$22,354/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+$1016万
+$21,955/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1050万
-$22,978/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
+$1172万
+$25,646/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$579万
-$23,160/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
+$569万
+$22,748/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$860万
-$26,641/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+$845万
+$26,167/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44754,38 +45173,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$694万
-$27,649/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
+$682万
+$27,155/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1063万
-$23,166/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+$1044万
+$22,752/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1226万
-$25,181/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+$1208万
+$24,807/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44793,39 +45212,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1029万
-$22,222/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+$1014万
+$21,890/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1044万
-$22,840/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
+$1058万
+$23,140/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$576万
-$23,024/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
+$567万
+$22,680/呎
+(24年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$753万
-$23,307/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+$742万
+$22,960/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44833,407 +45252,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$690万
-$27,482/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1201万
-$26,166/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1236万
-$25,382/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1026万
-$22,156/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1041万
-$22,772/呎
-(24年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$574万
-$22,952/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$772万
-$23,895/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$605万
-$24,116/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1054万
-$22,959/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1233万
-$25,322/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1023万
-$22,089/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1038万
-$22,705/呎
-(24年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$588万
-$23,536/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$748万
-$23,167/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$686万
-$27,319/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1080万
-$23,540/呎
-(22年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1230万
-$25,261/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1020万
-$22,022/呎
-(24年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1064万
-$23,280/呎
-(22年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$587万
-$23,464/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$746万
-$23,096/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$684万
-$27,239/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1048万
-$22,821/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1227万
-$25,201/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1016万
-$21,955/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1172万
-$25,646/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$569万
-$22,748/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$845万
-$26,167/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$682万
-$27,155/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1044万
-$22,752/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1208万
-$24,807/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1014万
-$21,890/呎
-(24年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1058万
-$23,140/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$567万
-$22,680/呎
-(24年-12月-04日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$742万
-$22,960/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$680万
-$27,076/呎
-(在售)</t>
+$598万
+$23,829/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -45876,27 +45900,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -46050,12 +46074,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -46137,12 +46161,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -46224,12 +46248,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -46311,12 +46335,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -47118,12 +47142,12 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
-$834万
-$26,312/呎
-(在售)</t>
+$734万
+$23,158/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -47790,12 +47814,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1664万
-$26,840/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -47877,12 +47901,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1659万
-$26,760/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -47964,12 +47988,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1654万
-$26,681/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -48051,12 +48075,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1649万
-$26,600/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -12168,7 +12168,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -18532,34 +18532,34 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>8605000</v>
+        <v>7573000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>26641</v>
+        <v>23446</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>7572400</v>
+        <v>7573000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>23444</v>
+        <v>23446</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -27562,38 +27562,30 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H419" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I419" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H419" s="5" t="n">
+        <v>11909000</v>
+      </c>
+      <c r="I419" s="5" t="n">
+        <v>25447</v>
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K419" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L419" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K419" s="5" t="n">
+        <v>11909000</v>
+      </c>
+      <c r="L419" s="5" t="n">
+        <v>25447</v>
       </c>
       <c r="M419" s="3" t="inlineStr">
         <is>
@@ -27602,7 +27594,7 @@
       </c>
       <c r="N419" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38638,7 +38630,7 @@
       </c>
       <c r="F597" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G597" s="3" t="inlineStr">
@@ -39258,7 +39250,7 @@
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G607" s="3" t="inlineStr">
@@ -39878,7 +39870,7 @@
       </c>
       <c r="F617" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G617" s="3" t="inlineStr">
@@ -40506,7 +40498,7 @@
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr">
@@ -41134,7 +41126,7 @@
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G637" s="3" t="inlineStr">
@@ -41762,7 +41754,7 @@
       </c>
       <c r="F647" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G647" s="3" t="inlineStr">
@@ -43771,17 +43763,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43885,12 +43877,12 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $682万
 $27,280/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -43964,20 +43956,20 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $680万
 $27,196/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $889万
 $27,533/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -44043,20 +44035,20 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $678万
 $27,116/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $887万
 $27,452/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -44122,20 +44114,20 @@
 (26年-07月-29日)</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $674万
 $26,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $881万
 $27,288/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -44201,20 +44193,20 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $672万
 $26,872/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $879万
 $27,207/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -44288,12 +44280,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $876万
 $27,124/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -44367,12 +44359,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $874万
 $27,043/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -44762,12 +44754,12 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$860万
-$26,641/呎
-(在售)</t>
+$757万
+$23,446/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -45900,17 +45892,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46082,12 +46074,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 468呎 (2房)
-招标单位
--
-(在售)</t>
+$1191万
+$25,447/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -47664,12 +47656,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $819万
 $25,845/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -47751,12 +47743,12 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $814万
 $25,691/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -47838,12 +47830,12 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $812万
 $25,612/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -47925,12 +47917,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $810万
 $25,536/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -48012,12 +48004,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $802万
 $25,284/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -48099,12 +48091,12 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $778万
 $24,549/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5237,14 +5237,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
         <v>10452000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>23330</v>
+        <v>23278</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>10452000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>23330</v>
+        <v>23278</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -16538,38 +16538,30 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="n">
+        <v>12568000</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>25807</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K247" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K247" s="5" t="n">
+        <v>12568000</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>25807</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
@@ -16578,7 +16570,7 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16807,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17389,7 +17381,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -37386,7 +37378,7 @@
         </is>
       </c>
       <c r="E577" s="4" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
@@ -37395,14 +37387,14 @@
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H577" s="5" t="n">
         <v>7253000</v>
       </c>
       <c r="I577" s="5" t="n">
-        <v>22880</v>
+        <v>22953</v>
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
@@ -37413,7 +37405,7 @@
         <v>7253000</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>22880</v>
+        <v>22953</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
@@ -42789,10 +42781,10 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 448呎 (2房)
+          <t>F | 449呎 (2房)
 $1045万
-$23,330/呎
-(26年-08月-07日)</t>
+$23,278/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -43763,7 +43755,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43773,7 +43765,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44398,12 +44390,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
+$1257万
+$25,807/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -44522,7 +44514,7 @@
           <t>F | 323呎 (1房)
 $764万
 $23,659/呎
-(26年-08月-08日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -44601,7 +44593,7 @@
           <t>F | 323呎 (1房)
 $762万
 $23,588/呎
-(26年-08月-08日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -47484,10 +47476,10 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>D | 317呎 (1房)
+          <t>D | 316呎 (1房)
 $725万
-$22,880/呎
-(26年-08月-05日)</t>
+$22,953/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -19103,7 +19103,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -24008,38 +24008,30 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H364" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I364" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H364" s="5" t="n">
+        <v>12143000</v>
+      </c>
+      <c r="I364" s="5" t="n">
+        <v>24934</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K364" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L364" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K364" s="5" t="n">
+        <v>12143000</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>24934</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -24048,7 +24040,7 @@
       </c>
       <c r="N364" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43755,7 +43747,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43765,7 +43757,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44830,7 +44822,7 @@
           <t>F | 323呎 (1房)
 $753万
 $23,307/呎
-(26年-08月-07日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -45417,12 +45409,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
+$1214万
+$24,934/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -34890,7 +34890,7 @@
         </is>
       </c>
       <c r="E537" s="4" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>7341000</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>23158</v>
+        <v>23231</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>7341000</v>
       </c>
       <c r="L537" s="5" t="n">
-        <v>23158</v>
+        <v>23231</v>
       </c>
       <c r="M537" s="3" t="inlineStr">
         <is>
@@ -40040,38 +40040,30 @@
       </c>
       <c r="F620" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H620" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I620" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="n">
+        <v>14667000</v>
+      </c>
+      <c r="I620" s="5" t="n">
+        <v>23656</v>
       </c>
       <c r="J620" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K620" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L620" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K620" s="5" t="n">
+        <v>14667000</v>
+      </c>
+      <c r="L620" s="5" t="n">
+        <v>23656</v>
       </c>
       <c r="M620" s="3" t="inlineStr">
         <is>
@@ -40080,7 +40072,7 @@
       </c>
       <c r="N620" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -45876,7 +45868,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45886,7 +45878,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47120,9 +47112,9 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>D | 317呎 (1房)
+          <t>D | 316呎 (1房)
 $734万
-$23,158/呎
+$23,231/呎
 (26年-08月-23日)</t>
         </is>
       </c>
@@ -47790,12 +47782,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1467万
+$23,656/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
